--- a/SGC-CKN/Excel/560c0633-ab66-4141-a3bf-7db70e2fd0d0_Hạng_mục_Lô_CT-02_P1-155_D800_08-14-2026.xlsx
+++ b/SGC-CKN/Excel/560c0633-ab66-4141-a3bf-7db70e2fd0d0_Hạng_mục_Lô_CT-02_P1-155_D800_08-14-2026.xlsx
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">07:20
-08/14/2026</t>
+08/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">07:45
-08/14/2026</t>
+08/04/2026</t>
   </si>
   <si>
     <t/>
@@ -116,7 +116,7 @@
   </si>
   <si>
     <t xml:space="preserve">08:30
-08/14/2026</t>
+08/04/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -126,7 +126,7 @@
   </si>
   <si>
     <t xml:space="preserve">09:00
-08/14/2026</t>
+08/04/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -136,7 +136,7 @@
   </si>
   <si>
     <t xml:space="preserve">09:40
-08/14/2026</t>
+08/04/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -146,7 +146,7 @@
   </si>
   <si>
     <t xml:space="preserve">11:00
-08/14/2026</t>
+08/04/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -156,7 +156,7 @@
   </si>
   <si>
     <t xml:space="preserve">13:30
-08/14/2026</t>
+08/04/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -166,11 +166,11 @@
   </si>
   <si>
     <t xml:space="preserve">15:30
-08/14/2026</t>
+08/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">15:43
-08/14/2026</t>
+08/04/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -180,7 +180,7 @@
   </si>
   <si>
     <t xml:space="preserve">18:20
-08/14/2026</t>
+08/04/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -1362,16 +1362,16 @@
         <v>-29</v>
       </c>
       <c r="G17" s="25">
-        <v>-32.15</v>
+        <v>-39.15</v>
       </c>
       <c r="H17" s="25">
         <v>0.22</v>
       </c>
       <c r="I17" s="25">
-        <v>3.15</v>
+        <v>10.15</v>
       </c>
       <c r="J17" s="8">
-        <v>14.54</v>
+        <v>46.85</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1394,7 +1394,7 @@
         <v>52</v>
       </c>
       <c r="F18" s="28">
-        <v>-32.15</v>
+        <v>-39.15</v>
       </c>
       <c r="G18" s="28">
         <v>-43.95</v>
@@ -1403,10 +1403,10 @@
         <v>2.62</v>
       </c>
       <c r="I18" s="28">
-        <v>11.8</v>
+        <v>4.8</v>
       </c>
       <c r="J18" s="12">
-        <v>4.51</v>
+        <v>1.83</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1738,16 +1738,16 @@
         <v>-29</v>
       </c>
       <c r="F8" s="25">
-        <v>-32.15</v>
+        <v>-39.15</v>
       </c>
       <c r="G8" s="25">
         <v>0.22</v>
       </c>
       <c r="H8" s="25">
-        <v>3.15</v>
+        <v>10.15</v>
       </c>
       <c r="I8" s="8">
-        <v>14.54</v>
+        <v>46.85</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1764,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-32.15</v>
+        <v>-39.15</v>
       </c>
       <c r="F9" s="28">
         <v>-43.95</v>
@@ -1773,10 +1773,10 @@
         <v>2.62</v>
       </c>
       <c r="H9" s="28">
-        <v>11.8</v>
+        <v>4.8</v>
       </c>
       <c r="I9" s="12">
-        <v>4.51</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">

--- a/SGC-CKN/Excel/560c0633-ab66-4141-a3bf-7db70e2fd0d0_Hạng_mục_Lô_CT-02_P1-155_D800_08-14-2026.xlsx
+++ b/SGC-CKN/Excel/560c0633-ab66-4141-a3bf-7db70e2fd0d0_Hạng_mục_Lô_CT-02_P1-155_D800_08-14-2026.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>07:20 08/14/2026</t>
+    <t>07:20 08/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>18:20 08/14/2026</t>
+    <t>18:20 08/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
